--- a/data/trans_orig/IP15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>27636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>45921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>82321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94094</t>
+          <t>94037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68839</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83025</t>
+          <t>81702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156366</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173208</t>
+          <t>174262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28999</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46048</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>61557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73633</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>73321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127311</t>
+          <t>126772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144360</t>
+          <t>144270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>43086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70060</t>
+          <t>70903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83404</t>
+          <t>83837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124754</t>
+          <t>123638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141370</t>
+          <t>141261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46773</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88751</t>
+          <t>90035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153960</t>
+          <t>152726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171670</t>
+          <t>170606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152861</t>
+          <t>153335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171595</t>
+          <t>172079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314056</t>
+          <t>312772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339460</t>
+          <t>337570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78065</t>
+          <t>78738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91025</t>
+          <t>90939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96148</t>
+          <t>95017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109779</t>
+          <t>109627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179135</t>
+          <t>178880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198472</t>
+          <t>197237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>61918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70765</t>
+          <t>70833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55355</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65595</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133883</t>
+          <t>134575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95070</t>
+          <t>95134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125736</t>
+          <t>126607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119932</t>
+          <t>119889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154385</t>
+          <t>151935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>222367</t>
+          <t>224229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>266568</t>
+          <t>270001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513120</t>
+          <t>512249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>543786</t>
+          <t>543722</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>532668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>564671</t>
+          <t>564714</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1056891</t>
+          <t>1053458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1101092</t>
+          <t>1099230</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>61588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74614</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73633</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126751</t>
+          <t>126145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146194</t>
+          <t>144175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62329</t>
+          <t>63214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76860</t>
+          <t>76589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78161</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89238</t>
+          <t>89239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145497</t>
+          <t>145966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162652</t>
+          <t>163407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>68807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79301</t>
+          <t>79404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79449</t>
+          <t>78989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141107</t>
+          <t>140719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155998</t>
+          <t>155531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71038</t>
+          <t>71063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>93542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122463</t>
+          <t>122881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147455</t>
+          <t>148127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167153</t>
+          <t>167477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157068</t>
+          <t>157043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179953</t>
+          <t>179637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311750</t>
+          <t>311332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340603</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>68439</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110728</t>
+          <t>112215</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128035</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104229</t>
+          <t>105046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120122</t>
+          <t>119830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220669</t>
+          <t>221787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243515</t>
+          <t>244247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41743</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>50371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52943</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>64324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98684</t>
+          <t>99394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112337</t>
+          <t>112886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123395</t>
+          <t>122558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157792</t>
+          <t>155563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,49 +5441,49 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>147286</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>130863</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>166239</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>23,25%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>130765</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>166175</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>409</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260898</t>
+          <t>264561</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311500</t>
+          <t>315596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>520752</t>
+          <t>522981</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>555149</t>
+          <t>555986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,47 +5554,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>81,94%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>567848</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>548895</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>584271</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>76,75%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>567848</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>548959</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>584369</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>79,4%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1082178</t>
+          <t>1078082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1132780</t>
+          <t>1129117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24785</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25152</t>
+          <t>25802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42914</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61021</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72521</t>
+          <t>72570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75012</t>
+          <t>75305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139973</t>
+          <t>139291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157735</t>
+          <t>157085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87261</t>
+          <t>87704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97779</t>
+          <t>98259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86800</t>
+          <t>86437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99414</t>
+          <t>99460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177847</t>
+          <t>178327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195023</t>
+          <t>194761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>26448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56441</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59691</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69588</t>
+          <t>69284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109985</t>
+          <t>110820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123819</t>
+          <t>124513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56407</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44921</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69197</t>
+          <t>69570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94942</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167170</t>
+          <t>166892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185864</t>
+          <t>185930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165933</t>
+          <t>166388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184155</t>
+          <t>184287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>339489</t>
+          <t>339497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365234</t>
+          <t>364861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>33973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +7425,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>52282</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>43261</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>65054</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>23,29%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>52282</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>41764</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>62819</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101121</t>
+          <t>100755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>116158</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109763</t>
+          <t>109115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124491</t>
+          <t>124335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +7538,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>76,26%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>227000</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>214228</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>236021</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>81,28%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>76,71%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>227000</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>216463</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>237518</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>81,28%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31470</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52783</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62127</t>
+          <t>62301</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97442</t>
+          <t>97720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112467</t>
+          <t>112637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108018</t>
+          <t>106902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140229</t>
+          <t>139568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100665</t>
+          <t>101506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133451</t>
+          <t>132486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216717</t>
+          <t>216296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262216</t>
+          <t>261147</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>531273</t>
+          <t>531934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>563484</t>
+          <t>564600</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>576286</t>
+          <t>577251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>609072</t>
+          <t>608231</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1119023</t>
+          <t>1120092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1164522</t>
+          <t>1164943</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>41047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44538</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>71264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86269</t>
+          <t>85981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95056</t>
+          <t>95154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113902</t>
+          <t>114175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171236</t>
+          <t>171618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196125</t>
+          <t>195367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>56950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64333</t>
+          <t>63171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77394</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64515</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132641</t>
+          <t>133304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153307</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39716</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>52664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79529</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95852</t>
+          <t>96067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127106</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43583</t>
+          <t>43324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69144</t>
+          <t>70161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104216</t>
+          <t>105037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203798</t>
+          <t>188538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90904</t>
+          <t>91910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166910</t>
+          <t>167854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149128</t>
+          <t>148111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174689</t>
+          <t>174948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232484</t>
+          <t>247744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332066</t>
+          <t>331245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37213</t>
+          <t>36917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>51981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78376</t>
+          <t>78274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>79012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93808</t>
+          <t>94041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116271</t>
+          <t>115282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137221</t>
+          <t>136864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>200170</t>
+          <t>200272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226310</t>
+          <t>226565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18612</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35829</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50283</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61052</t>
+          <t>61065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>48926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>61902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105069</t>
+          <t>104594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120917</t>
+          <t>120586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143737</t>
+          <t>147697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238947</t>
+          <t>245026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156070</t>
+          <t>157158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205397</t>
+          <t>200236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318556</t>
+          <t>319938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426792</t>
+          <t>431859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>414891</t>
+          <t>408812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>506141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>543122</t>
+          <t>548283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>592449</t>
+          <t>591361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>975565</t>
+          <t>970498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1083801</t>
+          <t>1082419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
